--- a/INSTANCES/instances_xlsx/A_MTN_3/262FL_10A_1.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_3/262FL_10A_1.xlsx
@@ -8637,7 +8637,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -8654,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -8671,7 +8671,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -8688,7 +8688,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -8705,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -8739,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -8756,7 +8756,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
